--- a/Result/checksun_type/磁碟儲存系統.xlsx
+++ b/Result/checksun_type/磁碟儲存系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>217717</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>149413</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>216732</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>221658</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>301588</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>199194</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>216632</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>357016</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>609988</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>600689</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>797538</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>321219</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>681031</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>299.5</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>335.72</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>291.1</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>335.72</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>291.1</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>237601.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>202459.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>202459</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>215506.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>238149.84</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>238149.84</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-13639.24515680911</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>237601</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>237601.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>297.3</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>338.78</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>289.81</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>338.78</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>289.81</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>297025.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>226007.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>226007.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>196759.0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>234662.14</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>234662.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-16479.09839787419</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>297025</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>297025.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>296.6</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>341.25</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>288.46</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>341.25</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>288.46</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>135729.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>293694.2</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>293694.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>172876.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>232143.94</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>232143.94</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-26314.34951375733</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>135729</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>135729.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>305.5</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>342.92</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>287.46</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>342.92</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>287.46</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>182641.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>277999.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>277999.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>180004.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>232519.28</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>232519.28</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-22143.19576809907</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>182641</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>182641.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>313.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>343.2</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>286.79</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>286.79</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>159299.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>250426.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>250426</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>166481.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>229642.46</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>229642.46</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-20419.8619968695</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>159299</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>159299.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>321.9</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>341.88</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>286.08</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>341.88</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>286.08</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>355345.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>228553.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>228553.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>156708.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>227652.22</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>227652.22</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-14727.74725236758</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>355345</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>355345.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>331.3</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>340.42</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>285.31</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>340.42</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>285.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>635457.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>167510.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>167510.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>136013.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>221077.8</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>221077.8</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-27075.09235835169</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>635457</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>635457.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>337.5</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>338.42</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>284.24</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>338.42</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>284.24</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>57256.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>52059.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>52059.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>94425.4</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>209271.1</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>209271.1</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-73759.18921124504</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>57256</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>57256.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>336.9</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>334.9</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>282.46</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>282.46</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>44773.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>82010.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>82010.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>122404.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>210068.08</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>210068.08</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-75866.39224354818</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>44773</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>44773.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>344.0</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>331.18</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>280.92</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>331.18</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>280.92</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>49936.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>82536.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>82536.60000000001</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>153095.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>211943.66</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>211943.66</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-74829.70399528308</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>49936</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>49936.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>350.6</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>326.82</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>279.51</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>326.82</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>279.51</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>50129.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>84864.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>84864.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>180469.5</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>212547.1</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>212547.1</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-71229.40992650142</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>50129</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>50129.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>26.64</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>27.42</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>29.76</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>29.76</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>12947.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>26318.2</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>26318.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>16294.9</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>14302.9</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>14302.9</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>2116.636459194189</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>12947</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>12947.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>26.39</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>27.5</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>29.96</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>7393.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>24633.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>24633.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>15669.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>20401.14</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>20401.14</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>2926.220914931811</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>7393</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>7393.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>26.35</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>27.64</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>30.15</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>27.64</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>30.15</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>24831.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>24790.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>24790</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>15333.6</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>22624.02</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>22624.02</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>4573.333676166567</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>24831</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>24831.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>26.45</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>27.8</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>30.27</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>30.27</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>79020.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>21051.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>21051.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>13345.3</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>22455.72</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>22455.72</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>4894.661418067404</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>79020</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>79020.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>26.68</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>27.94</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>30.4</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>7400.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>6357.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>6357.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>5915.9</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>21217.42</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>21217.42</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-627.0725727195168</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>7400</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>7400.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>26.96</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>28.09</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>30.52</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>30.52</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>4522.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>6271.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>6271.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>6117.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>21387.62</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>21387.62</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-819.2971105322777</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>4522</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>4522.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>27.4</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>28.29</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>30.66</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>30.66</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>8177.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>6705.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>6705.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>6223.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>22101.32</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>22101.32</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-756.2858391743566</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>8177</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>8177.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>27.71</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>28.44</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>30.8</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>6140.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>5877.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>5877.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>6394.0</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>22506.0</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>22506</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1030.866671549668</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>6140</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>6140.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>27.82</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>28.56</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>30.92</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>30.92</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>5550.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>5638.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>5638.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>6264.0</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>23529.66</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>23529.66</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-1168.058336673341</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>5550</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>5550.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>27.87</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>31.07</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>28.68</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>31.07</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>6969.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>5474.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>5474</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>6321.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>24230.9</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>24230.9</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-1259.115774825967</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>6969</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>6969.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>27.84</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>28.77</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>31.24</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>28.77</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>31.24</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>6692.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>5963.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>5963</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>6185.9</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>24863.82</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>24863.82</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-1496.265123085936</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>6692</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>6692.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>13.84</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>13.74</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>12.19</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>12.19</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1916049.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>2230185.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>2230185.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>7855430.8</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>3287438.6</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>3287438.6</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-644125.9550543055</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1916049</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1916049.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>13.96</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>13.69</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>12.11</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>12.11</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>1648332.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>2526396.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>2526396.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>9316473.2</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>3267866.4</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>3267866.4</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-487655.5743637849</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>1648332</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>1648332.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>14.18</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>13.62</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>12.02</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>1285336.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>3266430.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>3266430.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>9632803.8</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>3262158.64</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>3262158.64</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-218026.224292906</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>1285336</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>1285336.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>14.47</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>13.57</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>11.95</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2956778.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>4817685.2</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>4817685.2</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>9767088.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>3255634.72</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>3255634.72</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>213837.6409616675</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2956778</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2956778.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>14.94</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>13.52</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>11.87</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>13.52</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>11.87</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>3344434.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>7508318.2</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>7508318.2</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>9580832.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>3216793.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>3216793</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>644065.8898624294</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>3344434</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>3344434.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>15.49</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>13.45</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>11.78</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>11.78</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>3397101.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>13480675.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>13480675.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>9309824.2</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>3166345.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>3166345</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>1194140.749368431</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>3397101</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>3397101.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>15.71</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>13.38</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>11.69</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>11.69</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>5348502.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>16106550.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>16106550.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>9039163.6</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>3146187.18</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>3146187.18</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>1931671.20047099</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>5348502</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>5348502.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>15.49</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>13.26</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>11.58</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>11.58</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>9041611.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>15999177.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>15999177.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>8603879.7</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>3060108.9</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>3060108.9</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>2707219.194886394</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>9041611</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>9041611.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>15.04</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>13.14</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>11.48</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>11.48</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>16409943.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>14716492.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>14716492.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>7783768.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2900811.26</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2900811.26</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>3322768.251376745</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>16409943</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>16409943.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>14.2</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>12.96</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>11.35</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>11.35</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>33206222.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>11653347.4</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>11653347.4</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>6223001.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2594833.24</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2594833.24</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>3293989.608813791</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>33206222</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>33206222.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>13.25</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>12.73</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>11.21</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>12.73</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>11.21</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>16526473.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>5138972.6</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>5138972.6</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>3008516.5</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>1988845.68</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>1988845.68</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>1335633.454837646</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>16526473</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>16526473.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>26.62</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>25.34</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>23.69</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>23.69</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>102372304.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>234746035.2</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>234746035.2</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>331777188.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>148368193.66</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>148368193.66</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-1243733.646371454</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>102372304</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>102372304.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>26.49</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>23.57</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>23.57</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>179935627.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>274122204.4</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>274122204.4</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>367893298.9</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>147137249.04</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>147137249.04</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>15677947.80682194</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>179935627</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>179935627.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>26.82999999999999</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>25.09</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>23.45</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>23.45</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>310086093.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>372706666.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>372706666.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>400411210.5</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>143895253.4</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>143895253.4</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>30981495.71114033</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>310086093</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>310086093.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>26.86</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>24.99</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>23.34</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>23.34</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>211944965.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>409465739.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>409465739.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>390988852.1</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>138001752.56</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>138001752.56</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>37792532.22762585</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>211944965</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>211944965.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>26.8</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>24.88</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>23.25</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>23.25</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>369391187.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>416927941.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>416927941.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>387369855.6</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>133984489.9</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>133984489.9</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>56687971.95733285</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>369391187</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>369391187.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>26.81</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>24.74</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>23.13</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>24.74</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>23.13</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>299253150.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>428808341.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>428808341.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>353423366.0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>126810093.98</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>126810093.98</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>64787648.78700948</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>299253150</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>299253150.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>26.96</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>24.68</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>23.05</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>672857937.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>461664393.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>461664393.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>325939999.4</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>120995653.96</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>120995653.96</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>81559560.76558298</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>672857937</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>672857937.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>26.61</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>24.56</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>22.91</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>22.91</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>493881457.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>428115754.6</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>428115754.6</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>261761793.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>107680989.18</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>107680989.18</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>62577509.24334568</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>493881457</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>493881457.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>26.25</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>24.39</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>22.79</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>22.79</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>249255976.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>372511965.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>372511965</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>214882943.7</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>98001199.46</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>98001199.45999999</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>52401433.16717285</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>249255976</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>249255976.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>25.86</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>24.23</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>22.69</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>22.69</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>428793186.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>357811769.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>357811769.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>192885048.4</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>93332529.68</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>93332529.68000001</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>62202574.83809844</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>428793186</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>428793186.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>25.0</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>24.02</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>22.58</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>22.58</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>463533411.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>278038390.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>278038390.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>154554582.1</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>84961649.4</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>84961649.40000001</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>54746555.62377432</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>463533411</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>463533411.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>2251806679</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2303990317</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>4282414081</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>3277325446</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>2111926901</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>2504000596</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>6330911536</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>3971577357</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2253776059</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>3252501668</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>3950855603</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
